--- a/docs/Mapping_casi_uso/matrimoni/Matr_007.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_007.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="323">
   <si>
     <t>Sezione</t>
   </si>
@@ -803,7 +803,10 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -812,7 +815,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -821,7 +824,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -830,7 +833,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -839,13 +842,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -854,7 +857,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -863,13 +866,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -878,7 +881,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dettagli evento</t>
@@ -938,13 +941,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1045,7 +1048,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.0546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7769,10 +7772,10 @@
         <v>261</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>262</v>
@@ -7789,7 +7792,7 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>90</v>
@@ -7798,7 +7801,7 @@
         <v>9</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>92</v>
@@ -7807,12 +7810,12 @@
         <v>10</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>93</v>
@@ -7821,7 +7824,7 @@
         <v>52</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>94</v>
@@ -7830,12 +7833,12 @@
         <v>10</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>95</v>
@@ -7844,7 +7847,7 @@
         <v>9</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>96</v>
@@ -7853,12 +7856,12 @@
         <v>10</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>97</v>
@@ -7867,7 +7870,7 @@
         <v>52</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>98</v>
@@ -7876,12 +7879,12 @@
         <v>10</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>99</v>
@@ -7890,7 +7893,7 @@
         <v>9</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>100</v>
@@ -7899,12 +7902,12 @@
         <v>10</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>101</v>
@@ -7913,7 +7916,7 @@
         <v>9</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>102</v>
@@ -7922,12 +7925,12 @@
         <v>10</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>103</v>
@@ -7936,7 +7939,7 @@
         <v>52</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>104</v>
@@ -7945,12 +7948,12 @@
         <v>10</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>105</v>
@@ -7959,7 +7962,7 @@
         <v>52</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>106</v>
@@ -7968,12 +7971,12 @@
         <v>10</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>107</v>
@@ -7982,7 +7985,7 @@
         <v>52</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>108</v>
@@ -7991,12 +7994,12 @@
         <v>10</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>109</v>
@@ -8005,7 +8008,7 @@
         <v>9</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>110</v>
@@ -8014,12 +8017,12 @@
         <v>10</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>111</v>
@@ -8028,7 +8031,7 @@
         <v>9</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>112</v>
@@ -8037,12 +8040,12 @@
         <v>10</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>113</v>
@@ -8051,7 +8054,7 @@
         <v>9</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>114</v>
@@ -8060,12 +8063,12 @@
         <v>10</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>115</v>
@@ -8074,7 +8077,7 @@
         <v>9</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>116</v>
@@ -8083,12 +8086,12 @@
         <v>10</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>117</v>
@@ -8097,7 +8100,7 @@
         <v>9</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>118</v>
@@ -8106,12 +8109,12 @@
         <v>10</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>119</v>
@@ -8120,7 +8123,7 @@
         <v>52</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>120</v>
@@ -8129,12 +8132,12 @@
         <v>10</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>121</v>
@@ -8143,7 +8146,7 @@
         <v>52</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>122</v>
@@ -8152,12 +8155,12 @@
         <v>10</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>123</v>
@@ -8166,7 +8169,7 @@
         <v>9</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>124</v>
@@ -8175,12 +8178,12 @@
         <v>10</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>125</v>
@@ -8189,7 +8192,7 @@
         <v>9</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>126</v>
@@ -8198,12 +8201,12 @@
         <v>10</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>127</v>
@@ -8212,7 +8215,7 @@
         <v>9</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>128</v>
@@ -8221,12 +8224,12 @@
         <v>10</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>129</v>
@@ -8235,7 +8238,7 @@
         <v>9</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>130</v>
@@ -8244,12 +8247,12 @@
         <v>10</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>131</v>
@@ -8258,7 +8261,7 @@
         <v>9</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>132</v>
@@ -8267,12 +8270,12 @@
         <v>10</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>133</v>
@@ -8281,7 +8284,7 @@
         <v>9</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>134</v>
@@ -8290,12 +8293,12 @@
         <v>10</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>135</v>
@@ -8304,7 +8307,7 @@
         <v>9</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>136</v>
@@ -8313,12 +8316,12 @@
         <v>10</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>137</v>
@@ -8327,7 +8330,7 @@
         <v>9</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>138</v>
@@ -8336,12 +8339,12 @@
         <v>10</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>139</v>
@@ -8350,7 +8353,7 @@
         <v>9</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>140</v>
@@ -8359,12 +8362,12 @@
         <v>10</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>141</v>
@@ -8373,7 +8376,7 @@
         <v>52</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>142</v>
@@ -8382,12 +8385,12 @@
         <v>10</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>143</v>
@@ -8396,7 +8399,7 @@
         <v>52</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>144</v>
@@ -8405,21 +8408,21 @@
         <v>10</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="C321" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>146</v>
@@ -8428,12 +8431,12 @@
         <v>10</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>90</v>
@@ -8442,7 +8445,7 @@
         <v>9</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>92</v>
@@ -8451,12 +8454,12 @@
         <v>10</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>93</v>
@@ -8465,7 +8468,7 @@
         <v>52</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>94</v>
@@ -8474,12 +8477,12 @@
         <v>10</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>95</v>
@@ -8488,7 +8491,7 @@
         <v>9</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>96</v>
@@ -8497,12 +8500,12 @@
         <v>10</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>97</v>
@@ -8511,7 +8514,7 @@
         <v>52</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>98</v>
@@ -8520,12 +8523,12 @@
         <v>10</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>99</v>
@@ -8534,7 +8537,7 @@
         <v>9</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>100</v>
@@ -8543,12 +8546,12 @@
         <v>10</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>101</v>
@@ -8557,7 +8560,7 @@
         <v>9</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>102</v>
@@ -8566,12 +8569,12 @@
         <v>10</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>103</v>
@@ -8580,7 +8583,7 @@
         <v>52</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>104</v>
@@ -8589,12 +8592,12 @@
         <v>10</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>105</v>
@@ -8603,7 +8606,7 @@
         <v>52</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>106</v>
@@ -8612,12 +8615,12 @@
         <v>10</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>107</v>
@@ -8626,7 +8629,7 @@
         <v>52</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>108</v>
@@ -8635,12 +8638,12 @@
         <v>10</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>109</v>
@@ -8649,7 +8652,7 @@
         <v>9</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>110</v>
@@ -8658,12 +8661,12 @@
         <v>10</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>111</v>
@@ -8672,7 +8675,7 @@
         <v>9</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>112</v>
@@ -8681,12 +8684,12 @@
         <v>10</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>113</v>
@@ -8695,7 +8698,7 @@
         <v>9</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>114</v>
@@ -8704,12 +8707,12 @@
         <v>10</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>115</v>
@@ -8718,7 +8721,7 @@
         <v>9</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>116</v>
@@ -8727,12 +8730,12 @@
         <v>10</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>117</v>
@@ -8741,7 +8744,7 @@
         <v>9</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>118</v>
@@ -8750,12 +8753,12 @@
         <v>10</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>119</v>
@@ -8764,7 +8767,7 @@
         <v>52</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>120</v>
@@ -8773,12 +8776,12 @@
         <v>10</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>121</v>
@@ -8787,7 +8790,7 @@
         <v>52</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>122</v>
@@ -8796,12 +8799,12 @@
         <v>10</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>123</v>
@@ -8810,7 +8813,7 @@
         <v>9</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>124</v>
@@ -8819,12 +8822,12 @@
         <v>10</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>125</v>
@@ -8833,7 +8836,7 @@
         <v>9</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>126</v>
@@ -8842,12 +8845,12 @@
         <v>10</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>127</v>
@@ -8856,7 +8859,7 @@
         <v>9</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>128</v>
@@ -8865,12 +8868,12 @@
         <v>10</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>129</v>
@@ -8879,7 +8882,7 @@
         <v>9</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>130</v>
@@ -8888,12 +8891,12 @@
         <v>10</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>131</v>
@@ -8902,7 +8905,7 @@
         <v>9</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>132</v>
@@ -8911,12 +8914,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>133</v>
@@ -8925,7 +8928,7 @@
         <v>9</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>134</v>
@@ -8934,12 +8937,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>135</v>
@@ -8948,7 +8951,7 @@
         <v>9</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>136</v>
@@ -8957,12 +8960,12 @@
         <v>10</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>137</v>
@@ -8971,7 +8974,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>138</v>
@@ -8980,12 +8983,12 @@
         <v>10</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>139</v>
@@ -8994,7 +8997,7 @@
         <v>9</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>140</v>
@@ -9003,12 +9006,12 @@
         <v>10</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>141</v>
@@ -9017,7 +9020,7 @@
         <v>52</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>142</v>
@@ -9026,12 +9029,12 @@
         <v>10</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>143</v>
@@ -9040,7 +9043,7 @@
         <v>52</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>144</v>
@@ -9049,21 +9052,21 @@
         <v>10</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>146</v>
@@ -9072,12 +9075,12 @@
         <v>10</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>90</v>
@@ -9086,7 +9089,7 @@
         <v>9</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>92</v>
@@ -9095,12 +9098,12 @@
         <v>10</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>93</v>
@@ -9109,7 +9112,7 @@
         <v>52</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>94</v>
@@ -9118,12 +9121,12 @@
         <v>10</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>95</v>
@@ -9132,7 +9135,7 @@
         <v>9</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>96</v>
@@ -9141,12 +9144,12 @@
         <v>10</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>97</v>
@@ -9155,7 +9158,7 @@
         <v>52</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>98</v>
@@ -9164,12 +9167,12 @@
         <v>10</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>99</v>
@@ -9178,7 +9181,7 @@
         <v>9</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>100</v>
@@ -9187,12 +9190,12 @@
         <v>10</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>101</v>
@@ -9201,7 +9204,7 @@
         <v>9</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>102</v>
@@ -9210,12 +9213,12 @@
         <v>10</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>103</v>
@@ -9224,7 +9227,7 @@
         <v>52</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>104</v>
@@ -9233,12 +9236,12 @@
         <v>10</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>105</v>
@@ -9247,7 +9250,7 @@
         <v>52</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>106</v>
@@ -9256,12 +9259,12 @@
         <v>10</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>107</v>
@@ -9270,7 +9273,7 @@
         <v>52</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>108</v>
@@ -9279,12 +9282,12 @@
         <v>10</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>109</v>
@@ -9293,7 +9296,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>110</v>
@@ -9302,12 +9305,12 @@
         <v>10</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>111</v>
@@ -9316,7 +9319,7 @@
         <v>9</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>112</v>
@@ -9325,12 +9328,12 @@
         <v>10</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>113</v>
@@ -9339,7 +9342,7 @@
         <v>9</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>114</v>
@@ -9348,12 +9351,12 @@
         <v>10</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>115</v>
@@ -9362,7 +9365,7 @@
         <v>9</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>116</v>
@@ -9371,12 +9374,12 @@
         <v>10</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>117</v>
@@ -9385,7 +9388,7 @@
         <v>9</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>118</v>
@@ -9394,12 +9397,12 @@
         <v>10</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>119</v>
@@ -9408,7 +9411,7 @@
         <v>52</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>120</v>
@@ -9417,12 +9420,12 @@
         <v>10</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>121</v>
@@ -9431,7 +9434,7 @@
         <v>52</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>122</v>
@@ -9440,12 +9443,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>123</v>
@@ -9454,7 +9457,7 @@
         <v>9</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>124</v>
@@ -9463,12 +9466,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>125</v>
@@ -9477,7 +9480,7 @@
         <v>9</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>126</v>
@@ -9486,12 +9489,12 @@
         <v>10</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>127</v>
@@ -9500,7 +9503,7 @@
         <v>9</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>128</v>
@@ -9509,12 +9512,12 @@
         <v>10</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>129</v>
@@ -9523,7 +9526,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>130</v>
@@ -9532,12 +9535,12 @@
         <v>10</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>131</v>
@@ -9546,7 +9549,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>132</v>
@@ -9555,12 +9558,12 @@
         <v>10</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>133</v>
@@ -9569,7 +9572,7 @@
         <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>134</v>
@@ -9578,12 +9581,12 @@
         <v>10</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>135</v>
@@ -9592,7 +9595,7 @@
         <v>9</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>136</v>
@@ -9601,12 +9604,12 @@
         <v>10</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>137</v>
@@ -9615,7 +9618,7 @@
         <v>9</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>138</v>
@@ -9624,12 +9627,12 @@
         <v>10</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>139</v>
@@ -9638,7 +9641,7 @@
         <v>9</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>140</v>
@@ -9647,12 +9650,12 @@
         <v>10</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>141</v>
@@ -9661,7 +9664,7 @@
         <v>52</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>142</v>
@@ -9670,12 +9673,12 @@
         <v>10</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>143</v>
@@ -9684,7 +9687,7 @@
         <v>52</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>144</v>
@@ -9693,21 +9696,21 @@
         <v>10</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>146</v>
@@ -9716,12 +9719,12 @@
         <v>10</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>90</v>
@@ -9730,7 +9733,7 @@
         <v>9</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>92</v>
@@ -9739,12 +9742,12 @@
         <v>10</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>93</v>
@@ -9753,7 +9756,7 @@
         <v>52</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>94</v>
@@ -9762,12 +9765,12 @@
         <v>10</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>95</v>
@@ -9776,7 +9779,7 @@
         <v>9</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>96</v>
@@ -9785,12 +9788,12 @@
         <v>10</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>97</v>
@@ -9799,7 +9802,7 @@
         <v>52</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>98</v>
@@ -9808,12 +9811,12 @@
         <v>10</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>99</v>
@@ -9822,7 +9825,7 @@
         <v>9</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>100</v>
@@ -9831,12 +9834,12 @@
         <v>10</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>101</v>
@@ -9845,7 +9848,7 @@
         <v>9</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>102</v>
@@ -9854,12 +9857,12 @@
         <v>10</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>103</v>
@@ -9868,7 +9871,7 @@
         <v>52</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>104</v>
@@ -9877,12 +9880,12 @@
         <v>10</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>105</v>
@@ -9891,7 +9894,7 @@
         <v>52</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>106</v>
@@ -9900,12 +9903,12 @@
         <v>10</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>107</v>
@@ -9914,7 +9917,7 @@
         <v>52</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>108</v>
@@ -9923,12 +9926,12 @@
         <v>10</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>109</v>
@@ -9937,7 +9940,7 @@
         <v>9</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>110</v>
@@ -9946,12 +9949,12 @@
         <v>10</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>111</v>
@@ -9960,7 +9963,7 @@
         <v>9</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>112</v>
@@ -9969,12 +9972,12 @@
         <v>10</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>113</v>
@@ -9983,7 +9986,7 @@
         <v>9</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>114</v>
@@ -9992,12 +9995,12 @@
         <v>10</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>115</v>
@@ -10006,7 +10009,7 @@
         <v>9</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>116</v>
@@ -10015,12 +10018,12 @@
         <v>10</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>117</v>
@@ -10029,7 +10032,7 @@
         <v>9</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>118</v>
@@ -10038,12 +10041,12 @@
         <v>10</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>119</v>
@@ -10052,7 +10055,7 @@
         <v>52</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>120</v>
@@ -10061,12 +10064,12 @@
         <v>10</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>121</v>
@@ -10075,7 +10078,7 @@
         <v>52</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>122</v>
@@ -10084,12 +10087,12 @@
         <v>10</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>123</v>
@@ -10098,7 +10101,7 @@
         <v>9</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>124</v>
@@ -10107,12 +10110,12 @@
         <v>10</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>125</v>
@@ -10121,7 +10124,7 @@
         <v>9</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>126</v>
@@ -10130,12 +10133,12 @@
         <v>10</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>127</v>
@@ -10144,7 +10147,7 @@
         <v>9</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>128</v>
@@ -10153,12 +10156,12 @@
         <v>10</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>129</v>
@@ -10167,7 +10170,7 @@
         <v>9</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>130</v>
@@ -10176,12 +10179,12 @@
         <v>10</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>131</v>
@@ -10190,7 +10193,7 @@
         <v>9</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>132</v>
@@ -10199,12 +10202,12 @@
         <v>10</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>133</v>
@@ -10213,7 +10216,7 @@
         <v>9</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>134</v>
@@ -10222,12 +10225,12 @@
         <v>10</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>135</v>
@@ -10236,7 +10239,7 @@
         <v>9</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>136</v>
@@ -10245,12 +10248,12 @@
         <v>10</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>137</v>
@@ -10259,7 +10262,7 @@
         <v>9</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>138</v>
@@ -10268,12 +10271,12 @@
         <v>10</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>139</v>
@@ -10282,7 +10285,7 @@
         <v>9</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>140</v>
@@ -10291,12 +10294,12 @@
         <v>10</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>141</v>
@@ -10305,7 +10308,7 @@
         <v>52</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>142</v>
@@ -10314,12 +10317,12 @@
         <v>10</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>143</v>
@@ -10328,7 +10331,7 @@
         <v>52</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>144</v>
@@ -10337,21 +10340,21 @@
         <v>10</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>146</v>
@@ -10360,12 +10363,12 @@
         <v>10</v>
       </c>
       <c r="G405" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>90</v>
@@ -10374,7 +10377,7 @@
         <v>9</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>92</v>
@@ -10383,12 +10386,12 @@
         <v>10</v>
       </c>
       <c r="G406" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>93</v>
@@ -10397,7 +10400,7 @@
         <v>52</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>94</v>
@@ -10406,12 +10409,12 @@
         <v>10</v>
       </c>
       <c r="G407" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>95</v>
@@ -10420,7 +10423,7 @@
         <v>9</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>96</v>
@@ -10429,12 +10432,12 @@
         <v>10</v>
       </c>
       <c r="G408" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>97</v>
@@ -10443,7 +10446,7 @@
         <v>52</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>98</v>
@@ -10452,12 +10455,12 @@
         <v>10</v>
       </c>
       <c r="G409" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>99</v>
@@ -10466,7 +10469,7 @@
         <v>9</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>100</v>
@@ -10475,12 +10478,12 @@
         <v>10</v>
       </c>
       <c r="G410" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>101</v>
@@ -10489,7 +10492,7 @@
         <v>9</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>102</v>
@@ -10498,12 +10501,12 @@
         <v>10</v>
       </c>
       <c r="G411" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>103</v>
@@ -10512,7 +10515,7 @@
         <v>52</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>104</v>
@@ -10521,12 +10524,12 @@
         <v>10</v>
       </c>
       <c r="G412" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>105</v>
@@ -10535,7 +10538,7 @@
         <v>52</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>106</v>
@@ -10544,12 +10547,12 @@
         <v>10</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>107</v>
@@ -10558,7 +10561,7 @@
         <v>52</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>108</v>
@@ -10567,12 +10570,12 @@
         <v>10</v>
       </c>
       <c r="G414" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>109</v>
@@ -10581,7 +10584,7 @@
         <v>9</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>110</v>
@@ -10590,12 +10593,12 @@
         <v>10</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>111</v>
@@ -10604,7 +10607,7 @@
         <v>9</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>112</v>
@@ -10613,12 +10616,12 @@
         <v>10</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>113</v>
@@ -10627,7 +10630,7 @@
         <v>9</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>114</v>
@@ -10636,12 +10639,12 @@
         <v>10</v>
       </c>
       <c r="G417" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>115</v>
@@ -10650,7 +10653,7 @@
         <v>9</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>116</v>
@@ -10659,12 +10662,12 @@
         <v>10</v>
       </c>
       <c r="G418" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>117</v>
@@ -10673,7 +10676,7 @@
         <v>9</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>118</v>
@@ -10682,12 +10685,12 @@
         <v>10</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>119</v>
@@ -10696,7 +10699,7 @@
         <v>52</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>120</v>
@@ -10705,12 +10708,12 @@
         <v>10</v>
       </c>
       <c r="G420" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>121</v>
@@ -10719,7 +10722,7 @@
         <v>52</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>122</v>
@@ -10728,12 +10731,12 @@
         <v>10</v>
       </c>
       <c r="G421" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>123</v>
@@ -10742,7 +10745,7 @@
         <v>9</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>124</v>
@@ -10751,12 +10754,12 @@
         <v>10</v>
       </c>
       <c r="G422" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>125</v>
@@ -10765,7 +10768,7 @@
         <v>9</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>126</v>
@@ -10774,12 +10777,12 @@
         <v>10</v>
       </c>
       <c r="G423" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>127</v>
@@ -10788,7 +10791,7 @@
         <v>9</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>128</v>
@@ -10797,12 +10800,12 @@
         <v>10</v>
       </c>
       <c r="G424" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>129</v>
@@ -10811,7 +10814,7 @@
         <v>9</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>130</v>
@@ -10820,12 +10823,12 @@
         <v>10</v>
       </c>
       <c r="G425" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>131</v>
@@ -10834,7 +10837,7 @@
         <v>9</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>132</v>
@@ -10843,12 +10846,12 @@
         <v>10</v>
       </c>
       <c r="G426" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>133</v>
@@ -10857,7 +10860,7 @@
         <v>9</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>134</v>
@@ -10866,12 +10869,12 @@
         <v>10</v>
       </c>
       <c r="G427" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>135</v>
@@ -10880,7 +10883,7 @@
         <v>9</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>136</v>
@@ -10889,12 +10892,12 @@
         <v>10</v>
       </c>
       <c r="G428" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>137</v>
@@ -10903,7 +10906,7 @@
         <v>9</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>138</v>
@@ -10912,12 +10915,12 @@
         <v>10</v>
       </c>
       <c r="G429" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>139</v>
@@ -10926,7 +10929,7 @@
         <v>9</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>140</v>
@@ -10935,12 +10938,12 @@
         <v>10</v>
       </c>
       <c r="G430" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>141</v>
@@ -10949,7 +10952,7 @@
         <v>52</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>142</v>
@@ -10958,12 +10961,12 @@
         <v>10</v>
       </c>
       <c r="G431" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>143</v>
@@ -10972,7 +10975,7 @@
         <v>52</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>144</v>
@@ -10981,21 +10984,21 @@
         <v>10</v>
       </c>
       <c r="G432" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>146</v>
@@ -11004,12 +11007,12 @@
         <v>10</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>214</v>
@@ -11018,7 +11021,7 @@
         <v>52</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>216</v>
@@ -11027,12 +11030,12 @@
         <v>10</v>
       </c>
       <c r="G434" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>218</v>
@@ -11041,7 +11044,7 @@
         <v>52</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>219</v>
@@ -11050,12 +11053,12 @@
         <v>10</v>
       </c>
       <c r="G435" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>220</v>
@@ -11064,7 +11067,7 @@
         <v>52</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>221</v>
@@ -11073,12 +11076,12 @@
         <v>10</v>
       </c>
       <c r="G436" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>222</v>
@@ -11087,7 +11090,7 @@
         <v>52</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>223</v>
@@ -11096,12 +11099,12 @@
         <v>10</v>
       </c>
       <c r="G437" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>224</v>
@@ -11110,7 +11113,7 @@
         <v>52</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>225</v>
@@ -11119,12 +11122,12 @@
         <v>10</v>
       </c>
       <c r="G438" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>226</v>
@@ -11133,7 +11136,7 @@
         <v>52</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>227</v>
@@ -11142,12 +11145,12 @@
         <v>10</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>228</v>
@@ -11156,7 +11159,7 @@
         <v>52</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>229</v>
@@ -11165,12 +11168,12 @@
         <v>10</v>
       </c>
       <c r="G440" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>90</v>
@@ -11179,7 +11182,7 @@
         <v>9</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>92</v>
@@ -11188,12 +11191,12 @@
         <v>10</v>
       </c>
       <c r="G441" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>93</v>
@@ -11202,7 +11205,7 @@
         <v>52</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>94</v>
@@ -11211,12 +11214,12 @@
         <v>10</v>
       </c>
       <c r="G442" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>95</v>
@@ -11225,7 +11228,7 @@
         <v>9</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>96</v>
@@ -11234,12 +11237,12 @@
         <v>10</v>
       </c>
       <c r="G443" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>97</v>
@@ -11248,7 +11251,7 @@
         <v>52</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>98</v>
@@ -11257,12 +11260,12 @@
         <v>10</v>
       </c>
       <c r="G444" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>99</v>
@@ -11271,7 +11274,7 @@
         <v>9</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>100</v>
@@ -11280,12 +11283,12 @@
         <v>10</v>
       </c>
       <c r="G445" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>101</v>
@@ -11294,7 +11297,7 @@
         <v>9</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>102</v>
@@ -11303,12 +11306,12 @@
         <v>10</v>
       </c>
       <c r="G446" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>103</v>
@@ -11317,7 +11320,7 @@
         <v>52</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>104</v>
@@ -11326,12 +11329,12 @@
         <v>10</v>
       </c>
       <c r="G447" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>105</v>
@@ -11340,7 +11343,7 @@
         <v>52</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>106</v>
@@ -11349,12 +11352,12 @@
         <v>10</v>
       </c>
       <c r="G448" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>107</v>
@@ -11363,7 +11366,7 @@
         <v>52</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>108</v>
@@ -11372,12 +11375,12 @@
         <v>10</v>
       </c>
       <c r="G449" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>109</v>
@@ -11386,7 +11389,7 @@
         <v>9</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>110</v>
@@ -11395,12 +11398,12 @@
         <v>10</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>111</v>
@@ -11409,7 +11412,7 @@
         <v>9</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>112</v>
@@ -11418,12 +11421,12 @@
         <v>10</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>113</v>
@@ -11432,7 +11435,7 @@
         <v>9</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>114</v>
@@ -11441,12 +11444,12 @@
         <v>10</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>115</v>
@@ -11455,7 +11458,7 @@
         <v>9</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>116</v>
@@ -11464,12 +11467,12 @@
         <v>10</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>117</v>
@@ -11478,7 +11481,7 @@
         <v>9</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>118</v>
@@ -11487,12 +11490,12 @@
         <v>10</v>
       </c>
       <c r="G454" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>119</v>
@@ -11501,7 +11504,7 @@
         <v>52</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>120</v>
@@ -11510,12 +11513,12 @@
         <v>10</v>
       </c>
       <c r="G455" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>121</v>
@@ -11524,7 +11527,7 @@
         <v>52</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>122</v>
@@ -11533,12 +11536,12 @@
         <v>10</v>
       </c>
       <c r="G456" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>123</v>
@@ -11547,7 +11550,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>124</v>
@@ -11556,12 +11559,12 @@
         <v>10</v>
       </c>
       <c r="G457" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>125</v>
@@ -11570,7 +11573,7 @@
         <v>9</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>126</v>
@@ -11579,12 +11582,12 @@
         <v>10</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>127</v>
@@ -11593,7 +11596,7 @@
         <v>9</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>128</v>
@@ -11602,12 +11605,12 @@
         <v>10</v>
       </c>
       <c r="G459" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>129</v>
@@ -11616,7 +11619,7 @@
         <v>9</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>130</v>
@@ -11625,12 +11628,12 @@
         <v>10</v>
       </c>
       <c r="G460" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>131</v>
@@ -11639,7 +11642,7 @@
         <v>9</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>132</v>
@@ -11648,12 +11651,12 @@
         <v>10</v>
       </c>
       <c r="G461" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>133</v>
@@ -11662,7 +11665,7 @@
         <v>9</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>134</v>
@@ -11671,12 +11674,12 @@
         <v>10</v>
       </c>
       <c r="G462" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>135</v>
@@ -11685,7 +11688,7 @@
         <v>9</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>136</v>
@@ -11694,12 +11697,12 @@
         <v>10</v>
       </c>
       <c r="G463" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>137</v>
@@ -11708,7 +11711,7 @@
         <v>9</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>138</v>
@@ -11717,12 +11720,12 @@
         <v>10</v>
       </c>
       <c r="G464" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>139</v>
@@ -11731,7 +11734,7 @@
         <v>9</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>140</v>
@@ -11740,12 +11743,12 @@
         <v>10</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>141</v>
@@ -11754,7 +11757,7 @@
         <v>52</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>142</v>
@@ -11763,12 +11766,12 @@
         <v>10</v>
       </c>
       <c r="G466" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>143</v>
@@ -11777,7 +11780,7 @@
         <v>52</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>144</v>
@@ -11786,21 +11789,21 @@
         <v>10</v>
       </c>
       <c r="G467" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>146</v>
@@ -11809,12 +11812,12 @@
         <v>10</v>
       </c>
       <c r="G468" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>90</v>
@@ -11823,7 +11826,7 @@
         <v>9</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>92</v>
@@ -11832,12 +11835,12 @@
         <v>10</v>
       </c>
       <c r="G469" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>93</v>
@@ -11846,7 +11849,7 @@
         <v>52</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>94</v>
@@ -11855,12 +11858,12 @@
         <v>10</v>
       </c>
       <c r="G470" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>95</v>
@@ -11869,7 +11872,7 @@
         <v>9</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>96</v>
@@ -11878,12 +11881,12 @@
         <v>10</v>
       </c>
       <c r="G471" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>97</v>
@@ -11892,7 +11895,7 @@
         <v>52</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>98</v>
@@ -11901,12 +11904,12 @@
         <v>10</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>99</v>
@@ -11915,7 +11918,7 @@
         <v>9</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>100</v>
@@ -11924,12 +11927,12 @@
         <v>10</v>
       </c>
       <c r="G473" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>101</v>
@@ -11938,7 +11941,7 @@
         <v>9</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>102</v>
@@ -11947,12 +11950,12 @@
         <v>10</v>
       </c>
       <c r="G474" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>103</v>
@@ -11961,7 +11964,7 @@
         <v>52</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>104</v>
@@ -11970,12 +11973,12 @@
         <v>10</v>
       </c>
       <c r="G475" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>105</v>
@@ -11984,7 +11987,7 @@
         <v>52</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>106</v>
@@ -11993,12 +11996,12 @@
         <v>10</v>
       </c>
       <c r="G476" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>107</v>
@@ -12007,7 +12010,7 @@
         <v>52</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>108</v>
@@ -12016,12 +12019,12 @@
         <v>10</v>
       </c>
       <c r="G477" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>109</v>
@@ -12030,7 +12033,7 @@
         <v>9</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>110</v>
@@ -12039,12 +12042,12 @@
         <v>10</v>
       </c>
       <c r="G478" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>111</v>
@@ -12053,7 +12056,7 @@
         <v>9</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>112</v>
@@ -12062,12 +12065,12 @@
         <v>10</v>
       </c>
       <c r="G479" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>113</v>
@@ -12076,7 +12079,7 @@
         <v>9</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>114</v>
@@ -12085,12 +12088,12 @@
         <v>10</v>
       </c>
       <c r="G480" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>115</v>
@@ -12099,7 +12102,7 @@
         <v>9</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>116</v>
@@ -12108,12 +12111,12 @@
         <v>10</v>
       </c>
       <c r="G481" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>117</v>
@@ -12122,7 +12125,7 @@
         <v>9</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>118</v>
@@ -12131,12 +12134,12 @@
         <v>10</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>119</v>
@@ -12145,7 +12148,7 @@
         <v>52</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>120</v>
@@ -12154,12 +12157,12 @@
         <v>10</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>121</v>
@@ -12168,7 +12171,7 @@
         <v>52</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>122</v>
@@ -12177,12 +12180,12 @@
         <v>10</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>123</v>
@@ -12191,7 +12194,7 @@
         <v>9</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>124</v>
@@ -12200,12 +12203,12 @@
         <v>10</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>125</v>
@@ -12214,7 +12217,7 @@
         <v>9</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>126</v>
@@ -12223,12 +12226,12 @@
         <v>10</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>127</v>
@@ -12237,7 +12240,7 @@
         <v>9</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>128</v>
@@ -12246,12 +12249,12 @@
         <v>10</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>129</v>
@@ -12260,7 +12263,7 @@
         <v>9</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>130</v>
@@ -12269,12 +12272,12 @@
         <v>10</v>
       </c>
       <c r="G488" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>131</v>
@@ -12283,7 +12286,7 @@
         <v>9</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>132</v>
@@ -12292,12 +12295,12 @@
         <v>10</v>
       </c>
       <c r="G489" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>133</v>
@@ -12306,7 +12309,7 @@
         <v>9</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>134</v>
@@ -12315,12 +12318,12 @@
         <v>10</v>
       </c>
       <c r="G490" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>135</v>
@@ -12329,7 +12332,7 @@
         <v>9</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>136</v>
@@ -12338,12 +12341,12 @@
         <v>10</v>
       </c>
       <c r="G491" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>137</v>
@@ -12352,7 +12355,7 @@
         <v>9</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>138</v>
@@ -12361,12 +12364,12 @@
         <v>10</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>139</v>
@@ -12375,7 +12378,7 @@
         <v>9</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>140</v>
@@ -12384,12 +12387,12 @@
         <v>10</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>141</v>
@@ -12398,7 +12401,7 @@
         <v>52</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>142</v>
@@ -12407,12 +12410,12 @@
         <v>10</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>143</v>
@@ -12421,7 +12424,7 @@
         <v>52</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>144</v>
@@ -12430,21 +12433,21 @@
         <v>10</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>146</v>
@@ -12453,12 +12456,12 @@
         <v>10</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>214</v>
@@ -12467,7 +12470,7 @@
         <v>52</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>216</v>
@@ -12476,12 +12479,12 @@
         <v>10</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>218</v>
@@ -12490,7 +12493,7 @@
         <v>52</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>219</v>
@@ -12499,12 +12502,12 @@
         <v>10</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>220</v>
@@ -12513,7 +12516,7 @@
         <v>52</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>221</v>
@@ -12522,12 +12525,12 @@
         <v>10</v>
       </c>
       <c r="G499" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>222</v>
@@ -12536,7 +12539,7 @@
         <v>52</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>223</v>
@@ -12545,12 +12548,12 @@
         <v>10</v>
       </c>
       <c r="G500" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>224</v>
@@ -12559,7 +12562,7 @@
         <v>52</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>225</v>
@@ -12568,12 +12571,12 @@
         <v>10</v>
       </c>
       <c r="G501" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>226</v>
@@ -12582,7 +12585,7 @@
         <v>52</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>227</v>
@@ -12591,12 +12594,12 @@
         <v>10</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>228</v>
@@ -12605,7 +12608,7 @@
         <v>52</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>229</v>
@@ -12614,15 +12617,15 @@
         <v>10</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>52</v>
@@ -12631,7 +12634,7 @@
         <v>75</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F504" s="2" t="s">
         <v>10</v>
@@ -12642,10 +12645,10 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>52</v>
@@ -12654,7 +12657,7 @@
         <v>75</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F505" s="2" t="s">
         <v>10</v>
@@ -12665,10 +12668,10 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>52</v>
@@ -12677,7 +12680,7 @@
         <v>75</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>10</v>
@@ -12688,10 +12691,10 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>52</v>
@@ -12700,7 +12703,7 @@
         <v>75</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F507" s="2" t="s">
         <v>10</v>
@@ -12711,10 +12714,10 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>52</v>
@@ -12723,7 +12726,7 @@
         <v>75</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F508" s="2" t="s">
         <v>10</v>
@@ -12734,10 +12737,10 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>52</v>
@@ -12746,7 +12749,7 @@
         <v>75</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F509" s="2" t="s">
         <v>10</v>
@@ -12757,10 +12760,10 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>52</v>
@@ -12769,7 +12772,7 @@
         <v>75</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>10</v>
@@ -12780,10 +12783,10 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>52</v>
@@ -12792,7 +12795,7 @@
         <v>248</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F511" s="2" t="s">
         <v>10</v>
@@ -12803,10 +12806,10 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>52</v>
@@ -12815,7 +12818,7 @@
         <v>248</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>10</v>
@@ -12826,10 +12829,10 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>9</v>
@@ -12838,10 +12841,10 @@
         <v>75</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F513" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G513" s="2" t="s">
         <v>55</v>
@@ -12849,10 +12852,10 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>9</v>
@@ -12861,7 +12864,7 @@
         <v>75</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F514" s="2" t="s">
         <v>10</v>
@@ -12872,19 +12875,19 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>10</v>
@@ -12895,19 +12898,19 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>10</v>
@@ -12918,19 +12921,19 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>10</v>
@@ -12941,19 +12944,19 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F518" s="2" t="s">
         <v>10</v>
